--- a/data/euro_curve.xlsx
+++ b/data/euro_curve.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/igorbykov/Desktop/Thesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{978CF1C8-90E1-D545-B6DD-418C0B8A28D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460505AE-91C3-4549-976A-F5B743EF7201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="580" windowWidth="27640" windowHeight="16680" xr2:uid="{41B76623-0F8C-CC4D-8254-74672EE5E301}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="6">
   <si>
     <t>15Y</t>
   </si>
@@ -432,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D6E87C9-80E4-564D-8954-5B2C07A25C53}">
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -1532,27 +1532,29 @@
       <c r="F46" s="1">
         <v>0.56200000000000006</v>
       </c>
-      <c r="G46" s="1"/>
+      <c r="G46" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H46" s="1"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>44834</v>
+        <v>44742</v>
       </c>
       <c r="B47" s="1">
-        <v>3.077</v>
+        <v>2.3439999999999999</v>
       </c>
       <c r="C47" s="1">
-        <v>2.93</v>
+        <v>2.0760000000000001</v>
       </c>
       <c r="D47" s="1">
-        <v>2.6059999999999999</v>
+        <v>1.552</v>
       </c>
       <c r="E47" s="1">
-        <v>2.41</v>
+        <v>1.2430000000000001</v>
       </c>
       <c r="F47" s="1">
-        <v>1.925</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>5</v>
@@ -1561,22 +1563,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>44804</v>
+        <v>44712</v>
       </c>
       <c r="B48" s="1">
-        <v>2.4820000000000002</v>
+        <v>1.9530000000000001</v>
       </c>
       <c r="C48" s="1">
-        <v>2.29</v>
+        <v>1.6970000000000001</v>
       </c>
       <c r="D48" s="1">
-        <v>1.9590000000000001</v>
+        <v>1.2090000000000001</v>
       </c>
       <c r="E48" s="1">
-        <v>1.825</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="F48" s="1">
-        <v>1.419</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>5</v>
@@ -1585,22 +1587,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>44771</v>
+        <v>44680</v>
       </c>
       <c r="B49" s="1">
-        <v>1.8109999999999999</v>
+        <v>1.766</v>
       </c>
       <c r="C49" s="1">
-        <v>1.5409999999999999</v>
+        <v>1.536</v>
       </c>
       <c r="D49" s="1">
-        <v>1.054</v>
+        <v>1.1160000000000001</v>
       </c>
       <c r="E49" s="1">
-        <v>0.83599999999999997</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="F49" s="1">
-        <v>0.56200000000000006</v>
+        <v>-4.2999999999999997E-2</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>5</v>
@@ -1609,22 +1611,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>44742</v>
+        <v>44651</v>
       </c>
       <c r="B50" s="1">
-        <v>2.3439999999999999</v>
+        <v>1.2569999999999999</v>
       </c>
       <c r="C50" s="1">
-        <v>2.0760000000000001</v>
+        <v>1.0680000000000001</v>
       </c>
       <c r="D50" s="1">
-        <v>1.552</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="E50" s="1">
-        <v>1.2430000000000001</v>
+        <v>0.495</v>
       </c>
       <c r="F50" s="1">
-        <v>0.52700000000000002</v>
+        <v>-0.39800000000000002</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>5</v>
@@ -1633,22 +1635,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>44712</v>
+        <v>44620</v>
       </c>
       <c r="B51" s="1">
-        <v>1.9530000000000001</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="C51" s="1">
-        <v>1.6970000000000001</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="D51" s="1">
-        <v>1.2090000000000001</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="E51" s="1">
-        <v>0.93899999999999995</v>
+        <v>0.02</v>
       </c>
       <c r="F51" s="1">
-        <v>0.17100000000000001</v>
+        <v>-0.67100000000000004</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>5</v>
@@ -1657,22 +1659,22 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>44680</v>
+        <v>44592</v>
       </c>
       <c r="B52" s="1">
-        <v>1.766</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="C52" s="1">
-        <v>1.536</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="D52" s="1">
-        <v>1.1160000000000001</v>
+        <v>-1.2E-2</v>
       </c>
       <c r="E52" s="1">
-        <v>0.86199999999999999</v>
+        <v>-0.21199999999999999</v>
       </c>
       <c r="F52" s="1">
-        <v>-4.2999999999999997E-2</v>
+        <v>-0.63</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>5</v>
@@ -1681,22 +1683,22 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>44651</v>
+        <v>44561</v>
       </c>
       <c r="B53" s="1">
-        <v>1.2569999999999999</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="C53" s="1">
-        <v>1.0680000000000001</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="D53" s="1">
-        <v>0.73299999999999998</v>
+        <v>-0.245</v>
       </c>
       <c r="E53" s="1">
-        <v>0.495</v>
+        <v>-0.41199999999999998</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.39800000000000002</v>
+        <v>-0.68300000000000005</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>5</v>
@@ -1705,22 +1707,22 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>44620</v>
+        <v>44530</v>
       </c>
       <c r="B54" s="1">
-        <v>0.91100000000000003</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="C54" s="1">
-        <v>0.67300000000000004</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D54" s="1">
-        <v>0.27400000000000002</v>
+        <v>-0.376</v>
       </c>
       <c r="E54" s="1">
-        <v>0.02</v>
+        <v>-0.51800000000000002</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.67100000000000004</v>
+        <v>-0.68899999999999995</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>5</v>
@@ -1729,22 +1731,22 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>44592</v>
+        <v>44498</v>
       </c>
       <c r="B55" s="1">
-        <v>0.56299999999999994</v>
+        <v>0.379</v>
       </c>
       <c r="C55" s="1">
-        <v>0.33700000000000002</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="D55" s="1">
-        <v>-1.2E-2</v>
+        <v>-0.14099999999999999</v>
       </c>
       <c r="E55" s="1">
-        <v>-0.21199999999999999</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.63</v>
+        <v>-0.56299999999999994</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>5</v>
@@ -1753,22 +1755,22 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>44561</v>
+        <v>44469</v>
       </c>
       <c r="B56" s="1">
-        <v>0.41399999999999998</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="C56" s="1">
-        <v>0.14799999999999999</v>
+        <v>6.3E-2</v>
       </c>
       <c r="D56" s="1">
-        <v>-0.245</v>
+        <v>-0.35099999999999998</v>
       </c>
       <c r="E56" s="1">
-        <v>-0.41199999999999998</v>
+        <v>-0.51</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.68300000000000005</v>
+        <v>-0.63200000000000001</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>5</v>
@@ -1777,22 +1779,22 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>44530</v>
+        <v>44439</v>
       </c>
       <c r="B57" s="1">
-        <v>0.25800000000000001</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="C57" s="1">
-        <v>6.0000000000000001E-3</v>
+        <v>-0.124</v>
       </c>
       <c r="D57" s="1">
-        <v>-0.376</v>
+        <v>-0.49</v>
       </c>
       <c r="E57" s="1">
-        <v>-0.51800000000000002</v>
+        <v>-0.58799999999999997</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.68899999999999995</v>
+        <v>-0.64300000000000002</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>5</v>
@@ -1801,22 +1803,22 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>44498</v>
+        <v>44407</v>
       </c>
       <c r="B58" s="1">
-        <v>0.379</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="C58" s="1">
-        <v>0.17199999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="D58" s="1">
-        <v>-0.14099999999999999</v>
+        <v>-0.51800000000000002</v>
       </c>
       <c r="E58" s="1">
-        <v>-0.28000000000000003</v>
+        <v>-0.60699999999999998</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.56299999999999994</v>
+        <v>-0.64600000000000002</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>5</v>
@@ -1825,22 +1827,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>44469</v>
+        <v>44377</v>
       </c>
       <c r="B59" s="1">
-        <v>0.38500000000000001</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="C59" s="1">
-        <v>6.3E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="D59" s="1">
-        <v>-0.35099999999999998</v>
+        <v>-0.372</v>
       </c>
       <c r="E59" s="1">
-        <v>-0.51</v>
+        <v>-0.52200000000000002</v>
       </c>
       <c r="F59" s="1">
-        <v>-0.63200000000000001</v>
+        <v>-0.629</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>5</v>
@@ -1849,22 +1851,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>44439</v>
+        <v>44347</v>
       </c>
       <c r="B60" s="1">
-        <v>0.21099999999999999</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="C60" s="1">
-        <v>-0.124</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="D60" s="1">
-        <v>-0.49</v>
+        <v>-0.36899999999999999</v>
       </c>
       <c r="E60" s="1">
-        <v>-0.58799999999999997</v>
+        <v>-0.52300000000000002</v>
       </c>
       <c r="F60" s="1">
-        <v>-0.64300000000000002</v>
+        <v>-0.61399999999999999</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>5</v>
@@ -1873,22 +1875,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>44407</v>
+        <v>44316</v>
       </c>
       <c r="B61" s="1">
-        <v>0.17199999999999999</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="C61" s="1">
-        <v>-0.16</v>
+        <v>1.4E-2</v>
       </c>
       <c r="D61" s="1">
-        <v>-0.51800000000000002</v>
+        <v>-0.41099999999999998</v>
       </c>
       <c r="E61" s="1">
-        <v>-0.60699999999999998</v>
+        <v>-0.55800000000000005</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.64600000000000002</v>
+        <v>-0.63800000000000001</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>5</v>
@@ -1897,22 +1899,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>44377</v>
+        <v>44286</v>
       </c>
       <c r="B62" s="1">
-        <v>0.39200000000000002</v>
+        <v>0.26</v>
       </c>
       <c r="C62" s="1">
-        <v>5.2999999999999999E-2</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D62" s="1">
-        <v>-0.372</v>
+        <v>-0.47599999999999998</v>
       </c>
       <c r="E62" s="1">
-        <v>-0.52200000000000002</v>
+        <v>-0.60099999999999998</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.629</v>
+        <v>-0.64200000000000002</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>5</v>
@@ -1921,22 +1923,22 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>44347</v>
+        <v>44253</v>
       </c>
       <c r="B63" s="1">
-        <v>0.39700000000000002</v>
+        <v>0.216</v>
       </c>
       <c r="C63" s="1">
-        <v>6.8000000000000005E-2</v>
+        <v>-8.4000000000000005E-2</v>
       </c>
       <c r="D63" s="1">
-        <v>-0.36899999999999999</v>
+        <v>-0.438</v>
       </c>
       <c r="E63" s="1">
-        <v>-0.52300000000000002</v>
+        <v>-0.57099999999999995</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.61399999999999999</v>
+        <v>-0.621</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>5</v>
@@ -1945,22 +1947,22 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>44316</v>
+        <v>44225</v>
       </c>
       <c r="B64" s="1">
-        <v>0.33900000000000002</v>
+        <v>-6.7000000000000004E-2</v>
       </c>
       <c r="C64" s="1">
-        <v>1.4E-2</v>
+        <v>-0.34699999999999998</v>
       </c>
       <c r="D64" s="1">
-        <v>-0.41099999999999998</v>
+        <v>-0.61099999999999999</v>
       </c>
       <c r="E64" s="1">
-        <v>-0.55800000000000005</v>
+        <v>-0.67100000000000004</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.63800000000000001</v>
+        <v>-0.66100000000000003</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>5</v>
@@ -1969,22 +1971,22 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>44286</v>
+        <v>44196</v>
       </c>
       <c r="B65" s="1">
-        <v>0.26</v>
+        <v>-0.14399999999999999</v>
       </c>
       <c r="C65" s="1">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.40500000000000003</v>
       </c>
       <c r="D65" s="1">
-        <v>-0.47599999999999998</v>
+        <v>-0.621</v>
       </c>
       <c r="E65" s="1">
-        <v>-0.60099999999999998</v>
+        <v>-0.65600000000000003</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.64200000000000002</v>
+        <v>-0.65600000000000003</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>5</v>
@@ -1993,22 +1995,22 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>44253</v>
+        <v>44165</v>
       </c>
       <c r="B66" s="1">
-        <v>0.216</v>
+        <v>-0.13</v>
       </c>
       <c r="C66" s="1">
-        <v>-8.4000000000000005E-2</v>
+        <v>-0.38900000000000001</v>
       </c>
       <c r="D66" s="1">
-        <v>-0.438</v>
+        <v>-0.61299999999999999</v>
       </c>
       <c r="E66" s="1">
-        <v>-0.57099999999999995</v>
+        <v>-0.65500000000000003</v>
       </c>
       <c r="F66" s="1">
-        <v>-0.621</v>
+        <v>-0.65</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>5</v>
@@ -2017,22 +2019,22 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>44225</v>
+        <v>44134</v>
       </c>
       <c r="B67" s="1">
-        <v>-6.7000000000000004E-2</v>
+        <v>-8.3000000000000004E-2</v>
       </c>
       <c r="C67" s="1">
-        <v>-0.34699999999999998</v>
+        <v>-0.34300000000000003</v>
       </c>
       <c r="D67" s="1">
-        <v>-0.61099999999999999</v>
+        <v>-0.59199999999999997</v>
       </c>
       <c r="E67" s="1">
-        <v>-0.67100000000000004</v>
+        <v>-0.64600000000000002</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.66100000000000003</v>
+        <v>-0.65</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>5</v>
@@ -2041,22 +2043,22 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>44196</v>
+        <v>44104</v>
       </c>
       <c r="B68" s="1">
-        <v>-0.14399999999999999</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="C68" s="1">
-        <v>-0.40500000000000003</v>
+        <v>-0.19900000000000001</v>
       </c>
       <c r="D68" s="1">
-        <v>-0.621</v>
+        <v>-0.48599999999999999</v>
       </c>
       <c r="E68" s="1">
-        <v>-0.65600000000000003</v>
+        <v>-0.55800000000000005</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.65600000000000003</v>
+        <v>-0.58599999999999997</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>5</v>
@@ -2065,22 +2067,22 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>44165</v>
+        <v>44074</v>
       </c>
       <c r="B69" s="1">
-        <v>-0.13</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="C69" s="1">
-        <v>-0.38900000000000001</v>
+        <v>-0.10100000000000001</v>
       </c>
       <c r="D69" s="1">
-        <v>-0.61299999999999999</v>
+        <v>-0.41799999999999998</v>
       </c>
       <c r="E69" s="1">
-        <v>-0.65500000000000003</v>
+        <v>-0.503</v>
       </c>
       <c r="F69" s="1">
-        <v>-0.65</v>
+        <v>-0.54500000000000004</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>5</v>
@@ -2089,22 +2091,22 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>44134</v>
+        <v>44043</v>
       </c>
       <c r="B70" s="1">
-        <v>-8.3000000000000004E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C70" s="1">
-        <v>-0.34300000000000003</v>
+        <v>-0.21099999999999999</v>
       </c>
       <c r="D70" s="1">
-        <v>-0.59199999999999997</v>
+        <v>-0.46200000000000002</v>
       </c>
       <c r="E70" s="1">
-        <v>-0.64600000000000002</v>
+        <v>-0.52100000000000002</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.65</v>
+        <v>-0.53800000000000003</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>5</v>
@@ -2113,22 +2115,22 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>44104</v>
+        <v>44012</v>
       </c>
       <c r="B71" s="1">
-        <v>3.2000000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="C71" s="1">
-        <v>-0.19900000000000001</v>
+        <v>-0.161</v>
       </c>
       <c r="D71" s="1">
-        <v>-0.48599999999999999</v>
+        <v>-0.432</v>
       </c>
       <c r="E71" s="1">
-        <v>-0.55800000000000005</v>
+        <v>-0.5</v>
       </c>
       <c r="F71" s="1">
-        <v>-0.58599999999999997</v>
+        <v>-0.499</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>5</v>
@@ -2137,22 +2139,22 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>44074</v>
+        <v>43980</v>
       </c>
       <c r="B72" s="1">
-        <v>0.14199999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="C72" s="1">
-        <v>-0.10100000000000001</v>
+        <v>-7.3999999999999996E-2</v>
       </c>
       <c r="D72" s="1">
-        <v>-0.41799999999999998</v>
+        <v>-0.33300000000000002</v>
       </c>
       <c r="E72" s="1">
-        <v>-0.503</v>
+        <v>-0.40699999999999997</v>
       </c>
       <c r="F72" s="1">
-        <v>-0.54500000000000004</v>
+        <v>-0.38300000000000001</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>5</v>
@@ -2161,22 +2163,22 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>44043</v>
+        <v>43951</v>
       </c>
       <c r="B73" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="C73" s="1">
-        <v>-0.21099999999999999</v>
+        <v>-8.7999999999999995E-2</v>
       </c>
       <c r="D73" s="1">
-        <v>-0.46200000000000002</v>
+        <v>-0.34799999999999998</v>
       </c>
       <c r="E73" s="1">
-        <v>-0.52100000000000002</v>
+        <v>-0.42299999999999999</v>
       </c>
       <c r="F73" s="1">
-        <v>-0.53800000000000003</v>
+        <v>-0.39500000000000002</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>5</v>
@@ -2185,22 +2187,22 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>44012</v>
+        <v>43921</v>
       </c>
       <c r="B74" s="1">
-        <v>0.06</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="C74" s="1">
-        <v>-0.161</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="D74" s="1">
-        <v>-0.432</v>
+        <v>-0.253</v>
       </c>
       <c r="E74" s="1">
-        <v>-0.5</v>
+        <v>-0.36399999999999999</v>
       </c>
       <c r="F74" s="1">
-        <v>-0.499</v>
+        <v>-0.40400000000000003</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>5</v>
@@ -2209,22 +2211,22 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>43980</v>
+        <v>43889</v>
       </c>
       <c r="B75" s="1">
-        <v>0.128</v>
+        <v>-3.5000000000000003E-2</v>
       </c>
       <c r="C75" s="1">
-        <v>-7.3999999999999996E-2</v>
+        <v>-0.25800000000000001</v>
       </c>
       <c r="D75" s="1">
-        <v>-0.33300000000000002</v>
+        <v>-0.49199999999999999</v>
       </c>
       <c r="E75" s="1">
-        <v>-0.40699999999999997</v>
+        <v>-0.55800000000000005</v>
       </c>
       <c r="F75" s="1">
-        <v>-0.38300000000000001</v>
+        <v>-0.57499999999999996</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>5</v>
@@ -2233,22 +2235,22 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>43951</v>
+        <v>43861</v>
       </c>
       <c r="B76" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.113</v>
       </c>
       <c r="C76" s="1">
-        <v>-8.7999999999999995E-2</v>
+        <v>-0.14299999999999999</v>
       </c>
       <c r="D76" s="1">
-        <v>-0.34799999999999998</v>
+        <v>-0.42199999999999999</v>
       </c>
       <c r="E76" s="1">
-        <v>-0.42299999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="F76" s="1">
-        <v>-0.39500000000000002</v>
+        <v>-0.52500000000000002</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>5</v>
@@ -2257,22 +2259,22 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>43921</v>
+        <v>43830</v>
       </c>
       <c r="B77" s="1">
-        <v>0.28499999999999998</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="C77" s="1">
-        <v>5.8000000000000003E-2</v>
+        <v>0.13</v>
       </c>
       <c r="D77" s="1">
-        <v>-0.253</v>
+        <v>-0.23400000000000001</v>
       </c>
       <c r="E77" s="1">
-        <v>-0.36399999999999999</v>
+        <v>-0.373</v>
       </c>
       <c r="F77" s="1">
-        <v>-0.40400000000000003</v>
+        <v>-0.47299999999999998</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>5</v>
@@ -2281,22 +2283,22 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>43889</v>
+        <v>43798</v>
       </c>
       <c r="B78" s="1">
-        <v>-3.5000000000000003E-2</v>
+        <v>0.253</v>
       </c>
       <c r="C78" s="1">
-        <v>-0.25800000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="D78" s="1">
-        <v>-0.49199999999999999</v>
+        <v>-0.34599999999999997</v>
       </c>
       <c r="E78" s="1">
-        <v>-0.55800000000000005</v>
+        <v>-0.44500000000000001</v>
       </c>
       <c r="F78" s="1">
-        <v>-0.57499999999999996</v>
+        <v>-0.48599999999999999</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>5</v>
@@ -2305,22 +2307,22 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>43861</v>
+        <v>43769</v>
       </c>
       <c r="B79" s="1">
-        <v>0.113</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="C79" s="1">
-        <v>-0.14299999999999999</v>
+        <v>-6.9000000000000006E-2</v>
       </c>
       <c r="D79" s="1">
-        <v>-0.42199999999999999</v>
+        <v>-0.38700000000000001</v>
       </c>
       <c r="E79" s="1">
-        <v>-0.5</v>
+        <v>-0.48699999999999999</v>
       </c>
       <c r="F79" s="1">
-        <v>-0.52500000000000002</v>
+        <v>-0.52</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>5</v>
@@ -2329,22 +2331,22 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>43830</v>
+        <v>43738</v>
       </c>
       <c r="B80" s="1">
-        <v>0.41499999999999998</v>
+        <v>1E-3</v>
       </c>
       <c r="C80" s="1">
-        <v>0.13</v>
+        <v>-0.255</v>
       </c>
       <c r="D80" s="1">
-        <v>-0.23400000000000001</v>
+        <v>-0.54800000000000004</v>
       </c>
       <c r="E80" s="1">
-        <v>-0.373</v>
+        <v>-0.61</v>
       </c>
       <c r="F80" s="1">
-        <v>-0.47299999999999998</v>
+        <v>-0.57799999999999996</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>5</v>
@@ -2353,22 +2355,22 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>43798</v>
+        <v>43707</v>
       </c>
       <c r="B81" s="1">
-        <v>0.253</v>
+        <v>-0.11600000000000001</v>
       </c>
       <c r="C81" s="1">
-        <v>-0.02</v>
+        <v>-0.376</v>
       </c>
       <c r="D81" s="1">
-        <v>-0.34599999999999997</v>
+        <v>-0.67500000000000004</v>
       </c>
       <c r="E81" s="1">
-        <v>-0.44500000000000001</v>
+        <v>-0.73299999999999998</v>
       </c>
       <c r="F81" s="1">
-        <v>-0.48599999999999999</v>
+        <v>-0.67</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>5</v>
@@ -2377,22 +2379,22 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>43769</v>
+        <v>43677</v>
       </c>
       <c r="B82" s="1">
-        <v>0.20399999999999999</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="C82" s="1">
-        <v>-6.9000000000000006E-2</v>
+        <v>-9.7000000000000003E-2</v>
       </c>
       <c r="D82" s="1">
-        <v>-0.38700000000000001</v>
+        <v>-0.501</v>
       </c>
       <c r="E82" s="1">
-        <v>-0.48699999999999999</v>
+        <v>-0.61599999999999999</v>
       </c>
       <c r="F82" s="1">
-        <v>-0.52</v>
+        <v>-0.627</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>5</v>
@@ -2401,22 +2403,22 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>43738</v>
+        <v>43644</v>
       </c>
       <c r="B83" s="1">
-        <v>1E-3</v>
+        <v>0.43</v>
       </c>
       <c r="C83" s="1">
-        <v>-0.255</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="D83" s="1">
-        <v>-0.54800000000000004</v>
+        <v>-0.39500000000000002</v>
       </c>
       <c r="E83" s="1">
-        <v>-0.61</v>
+        <v>-0.55200000000000005</v>
       </c>
       <c r="F83" s="1">
-        <v>-0.57799999999999996</v>
+        <v>-0.60499999999999998</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>5</v>
@@ -2425,22 +2427,22 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>43707</v>
+        <v>43616</v>
       </c>
       <c r="B84" s="1">
-        <v>-0.11600000000000001</v>
+        <v>0.63500000000000001</v>
       </c>
       <c r="C84" s="1">
-        <v>-0.376</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="D84" s="1">
-        <v>-0.67500000000000004</v>
+        <v>-0.26100000000000001</v>
       </c>
       <c r="E84" s="1">
-        <v>-0.73299999999999998</v>
+        <v>-0.43099999999999999</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.67</v>
+        <v>-0.52200000000000002</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>5</v>
@@ -2449,22 +2451,22 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>43677</v>
+        <v>43585</v>
       </c>
       <c r="B85" s="1">
-        <v>0.24099999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="C85" s="1">
-        <v>-9.7000000000000003E-2</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="D85" s="1">
-        <v>-0.501</v>
+        <v>-0.123</v>
       </c>
       <c r="E85" s="1">
-        <v>-0.61599999999999999</v>
+        <v>-0.32700000000000001</v>
       </c>
       <c r="F85" s="1">
-        <v>-0.627</v>
+        <v>-0.48099999999999998</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>5</v>
@@ -2473,22 +2475,22 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>43644</v>
+        <v>43553</v>
       </c>
       <c r="B86" s="1">
-        <v>0.43</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="C86" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="D86" s="1">
-        <v>-0.39500000000000002</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="E86" s="1">
-        <v>-0.55200000000000005</v>
+        <v>-0.34300000000000003</v>
       </c>
       <c r="F86" s="1">
-        <v>-0.60499999999999998</v>
+        <v>-0.47799999999999998</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>5</v>
@@ -2497,22 +2499,22 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>43616</v>
+        <v>43524</v>
       </c>
       <c r="B87" s="1">
-        <v>0.63500000000000001</v>
+        <v>1.032</v>
       </c>
       <c r="C87" s="1">
-        <v>0.23899999999999999</v>
+        <v>0.625</v>
       </c>
       <c r="D87" s="1">
-        <v>-0.26100000000000001</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="E87" s="1">
-        <v>-0.43099999999999999</v>
+        <v>-0.23899999999999999</v>
       </c>
       <c r="F87" s="1">
-        <v>-0.52200000000000002</v>
+        <v>-0.44400000000000001</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>5</v>
@@ -2521,22 +2523,22 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>43585</v>
+        <v>43496</v>
       </c>
       <c r="B88" s="1">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="C88" s="1">
-        <v>0.41899999999999998</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="D88" s="1">
-        <v>-0.123</v>
+        <v>-1.0999999999999999E-2</v>
       </c>
       <c r="E88" s="1">
-        <v>-0.32700000000000001</v>
+        <v>-0.26900000000000002</v>
       </c>
       <c r="F88" s="1">
-        <v>-0.48099999999999998</v>
+        <v>-0.45900000000000002</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>5</v>
@@ -2545,22 +2547,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>43553</v>
+        <v>43465</v>
       </c>
       <c r="B89" s="1">
-        <v>0.78500000000000003</v>
+        <v>1.111</v>
       </c>
       <c r="C89" s="1">
-        <v>0.38800000000000001</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="D89" s="1">
-        <v>-0.14000000000000001</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="E89" s="1">
-        <v>-0.34300000000000003</v>
+        <v>-0.28299999999999997</v>
       </c>
       <c r="F89" s="1">
-        <v>-0.47799999999999998</v>
+        <v>-0.46899999999999997</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>5</v>
@@ -2569,22 +2571,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>43524</v>
+        <v>43434</v>
       </c>
       <c r="B90" s="1">
-        <v>1.032</v>
+        <v>1.1379999999999999</v>
       </c>
       <c r="C90" s="1">
-        <v>0.625</v>
+        <v>0.749</v>
       </c>
       <c r="D90" s="1">
-        <v>1.7000000000000001E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="E90" s="1">
-        <v>-0.23899999999999999</v>
+        <v>-0.24099999999999999</v>
       </c>
       <c r="F90" s="1">
-        <v>-0.44400000000000001</v>
+        <v>-0.47499999999999998</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>5</v>
@@ -2593,22 +2595,22 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>43496</v>
+        <v>43404</v>
       </c>
       <c r="B91" s="1">
-        <v>0.99</v>
+        <v>1.167</v>
       </c>
       <c r="C91" s="1">
-        <v>0.60499999999999998</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="D91" s="1">
-        <v>-1.0999999999999999E-2</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="E91" s="1">
-        <v>-0.26900000000000002</v>
+        <v>-0.20899999999999999</v>
       </c>
       <c r="F91" s="1">
-        <v>-0.45900000000000002</v>
+        <v>-0.47799999999999998</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>5</v>
@@ -2617,22 +2619,22 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>43465</v>
+        <v>43371</v>
       </c>
       <c r="B92" s="1">
-        <v>1.111</v>
+        <v>1.1839999999999999</v>
       </c>
       <c r="C92" s="1">
-        <v>0.71599999999999997</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="D92" s="1">
-        <v>2.1999999999999999E-2</v>
+        <v>0.161</v>
       </c>
       <c r="E92" s="1">
-        <v>-0.28299999999999997</v>
+        <v>-0.18099999999999999</v>
       </c>
       <c r="F92" s="1">
-        <v>-0.46899999999999997</v>
+        <v>-0.48299999999999998</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>5</v>
@@ -2641,22 +2643,22 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>43434</v>
+        <v>43343</v>
       </c>
       <c r="B93" s="1">
-        <v>1.1379999999999999</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="C93" s="1">
-        <v>0.749</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="D93" s="1">
-        <v>7.5999999999999998E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="E93" s="1">
-        <v>-0.24099999999999999</v>
+        <v>-0.26500000000000001</v>
       </c>
       <c r="F93" s="1">
-        <v>-0.47499999999999998</v>
+        <v>-0.49</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>5</v>
@@ -2665,22 +2667,22 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>43404</v>
+        <v>43312</v>
       </c>
       <c r="B94" s="1">
-        <v>1.167</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="C94" s="1">
-        <v>0.78600000000000003</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="D94" s="1">
-        <v>0.11600000000000001</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="E94" s="1">
-        <v>-0.20899999999999999</v>
+        <v>-0.24199999999999999</v>
       </c>
       <c r="F94" s="1">
-        <v>-0.47799999999999998</v>
+        <v>-0.496</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>5</v>
@@ -2689,22 +2691,22 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>43371</v>
+        <v>43280</v>
       </c>
       <c r="B95" s="1">
-        <v>1.1839999999999999</v>
+        <v>1.0980000000000001</v>
       </c>
       <c r="C95" s="1">
-        <v>0.81299999999999994</v>
+        <v>0.69699999999999995</v>
       </c>
       <c r="D95" s="1">
-        <v>0.161</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="E95" s="1">
-        <v>-0.18099999999999999</v>
+        <v>-0.29299999999999998</v>
       </c>
       <c r="F95" s="1">
-        <v>-0.48299999999999998</v>
+        <v>-0.50900000000000001</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>5</v>
@@ -2713,22 +2715,22 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>43343</v>
+        <v>43251</v>
       </c>
       <c r="B96" s="1">
-        <v>1.0880000000000001</v>
+        <v>1.081</v>
       </c>
       <c r="C96" s="1">
-        <v>0.69499999999999995</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="D96" s="1">
-        <v>3.7999999999999999E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="E96" s="1">
-        <v>-0.26500000000000001</v>
+        <v>-0.27500000000000002</v>
       </c>
       <c r="F96" s="1">
-        <v>-0.49</v>
+        <v>-0.495</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>5</v>
@@ -2737,22 +2739,22 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>43312</v>
+        <v>43220</v>
       </c>
       <c r="B97" s="1">
-        <v>1.1499999999999999</v>
+        <v>1.1259999999999999</v>
       </c>
       <c r="C97" s="1">
-        <v>0.76500000000000001</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="D97" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.121</v>
       </c>
       <c r="E97" s="1">
-        <v>-0.24199999999999999</v>
+        <v>-0.24099999999999999</v>
       </c>
       <c r="F97" s="1">
-        <v>-0.496</v>
+        <v>-0.52900000000000003</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>5</v>
@@ -2761,22 +2763,22 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>43280</v>
+        <v>43189</v>
       </c>
       <c r="B98" s="1">
-        <v>1.0980000000000001</v>
+        <v>1.099</v>
       </c>
       <c r="C98" s="1">
-        <v>0.69699999999999995</v>
+        <v>0.74</v>
       </c>
       <c r="D98" s="1">
-        <v>2.1999999999999999E-2</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="E98" s="1">
-        <v>-0.29299999999999998</v>
+        <v>-0.26400000000000001</v>
       </c>
       <c r="F98" s="1">
-        <v>-0.50900000000000001</v>
+        <v>-0.53900000000000003</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>5</v>
@@ -2785,22 +2787,22 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>43251</v>
+        <v>43159</v>
       </c>
       <c r="B99" s="1">
-        <v>1.081</v>
+        <v>1.238</v>
       </c>
       <c r="C99" s="1">
-        <v>0.70699999999999996</v>
+        <v>0.86499999999999999</v>
       </c>
       <c r="D99" s="1">
-        <v>3.9E-2</v>
+        <v>0.189</v>
       </c>
       <c r="E99" s="1">
-        <v>-0.27500000000000002</v>
+        <v>-0.20499999999999999</v>
       </c>
       <c r="F99" s="1">
-        <v>-0.495</v>
+        <v>-0.52400000000000002</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>5</v>
@@ -2809,22 +2811,22 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>43220</v>
+        <v>43131</v>
       </c>
       <c r="B100" s="1">
-        <v>1.1259999999999999</v>
+        <v>1.2050000000000001</v>
       </c>
       <c r="C100" s="1">
-        <v>0.76800000000000002</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="D100" s="1">
-        <v>0.121</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="E100" s="1">
-        <v>-0.24099999999999999</v>
+        <v>-0.20599999999999999</v>
       </c>
       <c r="F100" s="1">
-        <v>-0.52900000000000003</v>
+        <v>-0.53500000000000003</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>5</v>
@@ -2833,22 +2835,22 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>43189</v>
+        <v>43098</v>
       </c>
       <c r="B101" s="1">
-        <v>1.099</v>
+        <v>0.97099999999999997</v>
       </c>
       <c r="C101" s="1">
-        <v>0.74</v>
+        <v>0.56100000000000005</v>
       </c>
       <c r="D101" s="1">
-        <v>8.8999999999999996E-2</v>
+        <v>-4.4999999999999998E-2</v>
       </c>
       <c r="E101" s="1">
-        <v>-0.26400000000000001</v>
+        <v>-0.33400000000000002</v>
       </c>
       <c r="F101" s="1">
-        <v>-0.53900000000000003</v>
+        <v>-0.56399999999999995</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>5</v>
@@ -2857,22 +2859,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>43159</v>
+        <v>43069</v>
       </c>
       <c r="B102" s="1">
-        <v>1.238</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="C102" s="1">
-        <v>0.86499999999999999</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="D102" s="1">
-        <v>0.189</v>
+        <v>-0.128</v>
       </c>
       <c r="E102" s="1">
-        <v>-0.20499999999999999</v>
+        <v>-0.39200000000000002</v>
       </c>
       <c r="F102" s="1">
-        <v>-0.52400000000000002</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>5</v>
@@ -2881,22 +2883,22 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>43131</v>
+        <v>43039</v>
       </c>
       <c r="B103" s="1">
-        <v>1.2050000000000001</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="C103" s="1">
-        <v>0.84499999999999997</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="D103" s="1">
-        <v>0.19700000000000001</v>
+        <v>-0.156</v>
       </c>
       <c r="E103" s="1">
-        <v>-0.20599999999999999</v>
+        <v>-0.41699999999999998</v>
       </c>
       <c r="F103" s="1">
-        <v>-0.53500000000000003</v>
+        <v>-0.57599999999999996</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>5</v>
@@ -2905,22 +2907,22 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>43098</v>
+        <v>43007</v>
       </c>
       <c r="B104" s="1">
-        <v>0.97099999999999997</v>
+        <v>1.095</v>
       </c>
       <c r="C104" s="1">
-        <v>0.56100000000000005</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="D104" s="1">
-        <v>-4.4999999999999998E-2</v>
+        <v>-7.4999999999999997E-2</v>
       </c>
       <c r="E104" s="1">
-        <v>-0.33400000000000002</v>
+        <v>-0.35299999999999998</v>
       </c>
       <c r="F104" s="1">
-        <v>-0.56399999999999995</v>
+        <v>-0.54300000000000004</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>5</v>
@@ -2929,22 +2931,22 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>43069</v>
+        <v>42978</v>
       </c>
       <c r="B105" s="1">
-        <v>0.93600000000000005</v>
+        <v>1.0069999999999999</v>
       </c>
       <c r="C105" s="1">
-        <v>0.51100000000000001</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="D105" s="1">
-        <v>-0.128</v>
+        <v>-0.155</v>
       </c>
       <c r="E105" s="1">
-        <v>-0.39200000000000002</v>
+        <v>-0.39300000000000002</v>
       </c>
       <c r="F105" s="1">
-        <v>-0.57999999999999996</v>
+        <v>-0.54100000000000004</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>5</v>
@@ -2953,22 +2955,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
-        <v>43039</v>
+        <v>42947</v>
       </c>
       <c r="B106" s="1">
-        <v>0.97499999999999998</v>
+        <v>1.1719999999999999</v>
       </c>
       <c r="C106" s="1">
-        <v>0.51900000000000002</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="D106" s="1">
-        <v>-0.156</v>
+        <v>-2.8000000000000001E-2</v>
       </c>
       <c r="E106" s="1">
-        <v>-0.41699999999999998</v>
+        <v>-0.31900000000000001</v>
       </c>
       <c r="F106" s="1">
-        <v>-0.57599999999999996</v>
+        <v>-0.53300000000000003</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>5</v>
@@ -2977,22 +2979,22 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
-        <v>43007</v>
+        <v>42916</v>
       </c>
       <c r="B107" s="1">
-        <v>1.095</v>
+        <v>1.1120000000000001</v>
       </c>
       <c r="C107" s="1">
-        <v>0.63200000000000001</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="D107" s="1">
-        <v>-7.4999999999999997E-2</v>
+        <v>-2.5999999999999999E-2</v>
       </c>
       <c r="E107" s="1">
-        <v>-0.35299999999999998</v>
+        <v>-0.29499999999999998</v>
       </c>
       <c r="F107" s="1">
-        <v>-0.54300000000000004</v>
+        <v>-0.51100000000000001</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>5</v>
@@ -3001,22 +3003,22 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
-        <v>42978</v>
+        <v>42886</v>
       </c>
       <c r="B108" s="1">
-        <v>1.0069999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="C108" s="1">
-        <v>0.53400000000000003</v>
+        <v>0.54</v>
       </c>
       <c r="D108" s="1">
-        <v>-0.155</v>
+        <v>-0.13900000000000001</v>
       </c>
       <c r="E108" s="1">
-        <v>-0.39300000000000002</v>
+        <v>-0.36499999999999999</v>
       </c>
       <c r="F108" s="1">
-        <v>-0.54100000000000004</v>
+        <v>-0.52600000000000002</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>5</v>
@@ -3025,22 +3027,22 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
-        <v>42947</v>
+        <v>42853</v>
       </c>
       <c r="B109" s="1">
-        <v>1.1719999999999999</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="C109" s="1">
-        <v>0.70199999999999996</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="D109" s="1">
-        <v>-2.8000000000000001E-2</v>
+        <v>-0.10199999999999999</v>
       </c>
       <c r="E109" s="1">
-        <v>-0.31900000000000001</v>
+        <v>-0.34200000000000003</v>
       </c>
       <c r="F109" s="1">
-        <v>-0.53300000000000003</v>
+        <v>-0.53200000000000003</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>5</v>
@@ -3049,22 +3051,22 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
-        <v>42916</v>
+        <v>42825</v>
       </c>
       <c r="B110" s="1">
-        <v>1.1120000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="C110" s="1">
-        <v>0.65600000000000003</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D110" s="1">
-        <v>-2.5999999999999999E-2</v>
+        <v>-0.106</v>
       </c>
       <c r="E110" s="1">
-        <v>-0.29499999999999998</v>
+        <v>-0.33400000000000002</v>
       </c>
       <c r="F110" s="1">
-        <v>-0.51100000000000001</v>
+        <v>-0.52700000000000002</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>5</v>
@@ -3073,19 +3075,19 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
-        <v>42886</v>
+        <v>42794</v>
       </c>
       <c r="B111" s="1">
-        <v>1.02</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="C111" s="1">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="D111" s="1">
-        <v>-0.13900000000000001</v>
+        <v>-0.21299999999999999</v>
       </c>
       <c r="E111" s="1">
-        <v>-0.36499999999999999</v>
+        <v>-0.39600000000000002</v>
       </c>
       <c r="F111" s="1">
         <v>-0.52600000000000002</v>
@@ -3097,22 +3099,22 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
-        <v>42853</v>
+        <v>42766</v>
       </c>
       <c r="B112" s="1">
-        <v>1.0169999999999999</v>
+        <v>1.026</v>
       </c>
       <c r="C112" s="1">
-        <v>0.55700000000000005</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="D112" s="1">
-        <v>-0.10199999999999999</v>
+        <v>-0.111</v>
       </c>
       <c r="E112" s="1">
-        <v>-0.34200000000000003</v>
+        <v>-0.34699999999999998</v>
       </c>
       <c r="F112" s="1">
-        <v>-0.53200000000000003</v>
+        <v>-0.52300000000000002</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>5</v>
@@ -3121,22 +3123,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
-        <v>42825</v>
+        <v>42734</v>
       </c>
       <c r="B113" s="1">
-        <v>1.01</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="C113" s="1">
-        <v>0.55000000000000004</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="D113" s="1">
-        <v>-0.106</v>
+        <v>-0.21299999999999999</v>
       </c>
       <c r="E113" s="1">
-        <v>-0.33400000000000002</v>
+        <v>-0.377</v>
       </c>
       <c r="F113" s="1">
-        <v>-0.52700000000000002</v>
+        <v>-0.497</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>5</v>
@@ -3145,22 +3147,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
-        <v>42794</v>
+        <v>42704</v>
       </c>
       <c r="B114" s="1">
-        <v>0.92500000000000004</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="C114" s="1">
-        <v>0.45</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="D114" s="1">
-        <v>-0.21299999999999999</v>
+        <v>-0.193</v>
       </c>
       <c r="E114" s="1">
-        <v>-0.39600000000000002</v>
+        <v>-0.36299999999999999</v>
       </c>
       <c r="F114" s="1">
-        <v>-0.52600000000000002</v>
+        <v>-0.46500000000000002</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>5</v>
@@ -3169,22 +3171,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
-        <v>42766</v>
+        <v>42674</v>
       </c>
       <c r="B115" s="1">
-        <v>1.026</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="C115" s="1">
-        <v>0.57299999999999995</v>
+        <v>0.224</v>
       </c>
       <c r="D115" s="1">
-        <v>-0.111</v>
+        <v>-0.26800000000000002</v>
       </c>
       <c r="E115" s="1">
-        <v>-0.34699999999999998</v>
+        <v>-0.378</v>
       </c>
       <c r="F115" s="1">
-        <v>-0.52300000000000002</v>
+        <v>-0.437</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>5</v>
@@ -3193,22 +3195,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
-        <v>42734</v>
+        <v>42643</v>
       </c>
       <c r="B116" s="1">
-        <v>0.84599999999999997</v>
+        <v>0.38</v>
       </c>
       <c r="C116" s="1">
-        <v>0.41299999999999998</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D116" s="1">
-        <v>-0.21299999999999999</v>
+        <v>-0.42599999999999999</v>
       </c>
       <c r="E116" s="1">
-        <v>-0.377</v>
+        <v>-0.45700000000000002</v>
       </c>
       <c r="F116" s="1">
-        <v>-0.497</v>
+        <v>-0.41799999999999998</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>5</v>
@@ -3217,22 +3219,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
-        <v>42704</v>
+        <v>42613</v>
       </c>
       <c r="B117" s="1">
-        <v>0.83499999999999996</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="C117" s="1">
-        <v>0.41599999999999998</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="D117" s="1">
-        <v>-0.193</v>
+        <v>-0.38100000000000001</v>
       </c>
       <c r="E117" s="1">
-        <v>-0.36299999999999999</v>
+        <v>-0.41899999999999998</v>
       </c>
       <c r="F117" s="1">
-        <v>-0.46500000000000002</v>
+        <v>-0.41099999999999998</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>5</v>
@@ -3241,22 +3243,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
-        <v>42674</v>
+        <v>42580</v>
       </c>
       <c r="B118" s="1">
-        <v>0.60099999999999998</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="C118" s="1">
-        <v>0.224</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="D118" s="1">
-        <v>-0.26800000000000002</v>
+        <v>-0.38100000000000001</v>
       </c>
       <c r="E118" s="1">
-        <v>-0.378</v>
+        <v>-0.433</v>
       </c>
       <c r="F118" s="1">
-        <v>-0.437</v>
+        <v>-0.40699999999999997</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>5</v>
@@ -3265,22 +3267,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
-        <v>42643</v>
+        <v>42551</v>
       </c>
       <c r="B119" s="1">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="C119" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="D119" s="1">
-        <v>-0.42599999999999999</v>
+        <v>-0.29899999999999999</v>
       </c>
       <c r="E119" s="1">
-        <v>-0.45700000000000002</v>
+        <v>-0.41399999999999998</v>
       </c>
       <c r="F119" s="1">
-        <v>-0.41799999999999998</v>
+        <v>-0.39800000000000002</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>5</v>
@@ -3289,22 +3291,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
-        <v>42613</v>
+        <v>42521</v>
       </c>
       <c r="B120" s="1">
-        <v>0.39700000000000002</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="C120" s="1">
-        <v>3.7999999999999999E-2</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="D120" s="1">
-        <v>-0.38100000000000001</v>
+        <v>-0.19500000000000001</v>
       </c>
       <c r="E120" s="1">
-        <v>-0.41899999999999998</v>
+        <v>-0.33500000000000002</v>
       </c>
       <c r="F120" s="1">
-        <v>-0.41099999999999998</v>
+        <v>-0.371</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>5</v>
@@ -3313,22 +3315,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
-        <v>42580</v>
+        <v>42489</v>
       </c>
       <c r="B121" s="1">
-        <v>0.48199999999999998</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="C121" s="1">
-        <v>8.1000000000000003E-2</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="D121" s="1">
-        <v>-0.38100000000000001</v>
+        <v>-0.114</v>
       </c>
       <c r="E121" s="1">
-        <v>-0.433</v>
+        <v>-0.28199999999999997</v>
       </c>
       <c r="F121" s="1">
-        <v>-0.40699999999999997</v>
+        <v>-0.32900000000000001</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>5</v>
@@ -3337,22 +3339,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
-        <v>42551</v>
+        <v>42460</v>
       </c>
       <c r="B122" s="1">
-        <v>0.67</v>
+        <v>0.89100000000000001</v>
       </c>
       <c r="C122" s="1">
-        <v>0.23799999999999999</v>
+        <v>0.434</v>
       </c>
       <c r="D122" s="1">
-        <v>-0.29899999999999999</v>
+        <v>-0.156</v>
       </c>
       <c r="E122" s="1">
-        <v>-0.41399999999999998</v>
+        <v>-0.30199999999999999</v>
       </c>
       <c r="F122" s="1">
-        <v>-0.39800000000000002</v>
+        <v>-0.32700000000000001</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>5</v>
@@ -3361,22 +3363,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
-        <v>42521</v>
+        <v>42429</v>
       </c>
       <c r="B123" s="1">
-        <v>0.90900000000000003</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="C123" s="1">
-        <v>0.41899999999999998</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="D123" s="1">
-        <v>-0.19500000000000001</v>
+        <v>-0.20599999999999999</v>
       </c>
       <c r="E123" s="1">
-        <v>-0.33500000000000002</v>
+        <v>-0.35299999999999998</v>
       </c>
       <c r="F123" s="1">
-        <v>-0.371</v>
+        <v>-0.34899999999999998</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>5</v>
@@ -3385,22 +3387,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
-        <v>42489</v>
+        <v>42398</v>
       </c>
       <c r="B124" s="1">
-        <v>1.0509999999999999</v>
+        <v>1.052</v>
       </c>
       <c r="C124" s="1">
-        <v>0.55200000000000005</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="D124" s="1">
-        <v>-0.114</v>
+        <v>-0.10100000000000001</v>
       </c>
       <c r="E124" s="1">
-        <v>-0.28199999999999997</v>
+        <v>-0.3</v>
       </c>
       <c r="F124" s="1">
-        <v>-0.32900000000000001</v>
+        <v>-0.32600000000000001</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>5</v>
@@ -3409,22 +3411,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
-        <v>42460</v>
+        <v>42369</v>
       </c>
       <c r="B125" s="1">
-        <v>0.89100000000000001</v>
+        <v>1.3480000000000001</v>
       </c>
       <c r="C125" s="1">
-        <v>0.434</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="D125" s="1">
-        <v>-0.156</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="E125" s="1">
-        <v>-0.30199999999999999</v>
+        <v>-0.13900000000000001</v>
       </c>
       <c r="F125" s="1">
-        <v>-0.32700000000000001</v>
+        <v>-0.221</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>5</v>
@@ -3433,22 +3435,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
-        <v>42429</v>
+        <v>42338</v>
       </c>
       <c r="B126" s="1">
-        <v>0.82699999999999996</v>
+        <v>1.226</v>
       </c>
       <c r="C126" s="1">
-        <v>0.38800000000000001</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="D126" s="1">
-        <v>-0.20599999999999999</v>
+        <v>-2.4E-2</v>
       </c>
       <c r="E126" s="1">
-        <v>-0.35299999999999998</v>
+        <v>-0.253</v>
       </c>
       <c r="F126" s="1">
-        <v>-0.34899999999999998</v>
+        <v>-0.27800000000000002</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>5</v>
@@ -3457,22 +3459,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
-        <v>42398</v>
+        <v>42307</v>
       </c>
       <c r="B127" s="1">
-        <v>1.052</v>
+        <v>1.2509999999999999</v>
       </c>
       <c r="C127" s="1">
-        <v>0.56899999999999995</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="D127" s="1">
-        <v>-0.10100000000000001</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="E127" s="1">
-        <v>-0.3</v>
+        <v>-0.14399999999999999</v>
       </c>
       <c r="F127" s="1">
-        <v>-0.32600000000000001</v>
+        <v>-0.21099999999999999</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>5</v>
@@ -3481,22 +3483,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
-        <v>42369</v>
+        <v>42277</v>
       </c>
       <c r="B128" s="1">
-        <v>1.3480000000000001</v>
+        <v>1.2909999999999999</v>
       </c>
       <c r="C128" s="1">
-        <v>0.83599999999999997</v>
+        <v>0.83899999999999997</v>
       </c>
       <c r="D128" s="1">
-        <v>0.11600000000000001</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="E128" s="1">
-        <v>-0.13900000000000001</v>
+        <v>-6.0999999999999999E-2</v>
       </c>
       <c r="F128" s="1">
-        <v>-0.221</v>
+        <v>-0.14699999999999999</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>5</v>
@@ -3505,22 +3507,22 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
-        <v>42338</v>
+        <v>42247</v>
       </c>
       <c r="B129" s="1">
-        <v>1.226</v>
+        <v>1.3109999999999999</v>
       </c>
       <c r="C129" s="1">
-        <v>0.70399999999999996</v>
+        <v>0.875</v>
       </c>
       <c r="D129" s="1">
-        <v>-2.4E-2</v>
+        <v>0.19</v>
       </c>
       <c r="E129" s="1">
-        <v>-0.253</v>
+        <v>-4.1000000000000002E-2</v>
       </c>
       <c r="F129" s="1">
-        <v>-0.27800000000000002</v>
+        <v>-0.13</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>5</v>
@@ -3529,22 +3531,22 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
-        <v>42307</v>
+        <v>42216</v>
       </c>
       <c r="B130" s="1">
-        <v>1.2509999999999999</v>
+        <v>1.2210000000000001</v>
       </c>
       <c r="C130" s="1">
-        <v>0.77700000000000002</v>
+        <v>0.80400000000000005</v>
       </c>
       <c r="D130" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="E130" s="1">
-        <v>-0.14399999999999999</v>
+        <v>-4.4999999999999998E-2</v>
       </c>
       <c r="F130" s="1">
-        <v>-0.21099999999999999</v>
+        <v>-0.11600000000000001</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>5</v>
@@ -3553,22 +3555,22 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
-        <v>42277</v>
+        <v>42185</v>
       </c>
       <c r="B131" s="1">
-        <v>1.2909999999999999</v>
+        <v>1.4239999999999999</v>
       </c>
       <c r="C131" s="1">
-        <v>0.83899999999999997</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="D131" s="1">
-        <v>0.17199999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="E131" s="1">
-        <v>-6.0999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="F131" s="1">
-        <v>-0.14699999999999999</v>
+        <v>-9.2999999999999999E-2</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>5</v>
@@ -3577,22 +3579,22 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
-        <v>42247</v>
+        <v>42153</v>
       </c>
       <c r="B132" s="1">
-        <v>1.3109999999999999</v>
+        <v>1.006</v>
       </c>
       <c r="C132" s="1">
-        <v>0.875</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="D132" s="1">
-        <v>0.19</v>
+        <v>0.114</v>
       </c>
       <c r="E132" s="1">
-        <v>-4.1000000000000002E-2</v>
+        <v>-5.3999999999999999E-2</v>
       </c>
       <c r="F132" s="1">
-        <v>-0.13</v>
+        <v>-0.104</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>5</v>
@@ -3601,22 +3603,22 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
-        <v>42216</v>
+        <v>42124</v>
       </c>
       <c r="B133" s="1">
-        <v>1.2210000000000001</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="C133" s="1">
-        <v>0.80400000000000005</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="D133" s="1">
-        <v>0.16500000000000001</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="E133" s="1">
-        <v>-4.4999999999999998E-2</v>
+        <v>-7.3999999999999996E-2</v>
       </c>
       <c r="F133" s="1">
-        <v>-0.11600000000000001</v>
+        <v>-0.104</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>5</v>
@@ -3625,22 +3627,22 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
-        <v>42185</v>
+        <v>42094</v>
       </c>
       <c r="B134" s="1">
-        <v>1.4239999999999999</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="C134" s="1">
-        <v>1.0009999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="D134" s="1">
-        <v>0.29199999999999998</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="E134" s="1">
-        <v>0.02</v>
+        <v>-0.13500000000000001</v>
       </c>
       <c r="F134" s="1">
-        <v>-9.2999999999999999E-2</v>
+        <v>-0.1</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>5</v>
@@ -3649,22 +3651,22 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
-        <v>42153</v>
+        <v>42062</v>
       </c>
       <c r="B135" s="1">
-        <v>1.006</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="C135" s="1">
-        <v>0.64800000000000002</v>
+        <v>0.46700000000000003</v>
       </c>
       <c r="D135" s="1">
-        <v>0.114</v>
+        <v>2E-3</v>
       </c>
       <c r="E135" s="1">
-        <v>-5.3999999999999999E-2</v>
+        <v>-9.8000000000000004E-2</v>
       </c>
       <c r="F135" s="1">
-        <v>-0.104</v>
+        <v>-7.9000000000000001E-2</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>5</v>
@@ -3673,22 +3675,22 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
-        <v>42124</v>
+        <v>42034</v>
       </c>
       <c r="B136" s="1">
-        <v>0.68600000000000005</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="C136" s="1">
-        <v>0.41399999999999998</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="D136" s="1">
+        <v>0.115</v>
+      </c>
+      <c r="E136" s="1">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="E136" s="1">
-        <v>-7.3999999999999996E-2</v>
-      </c>
       <c r="F136" s="1">
-        <v>-0.104</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>5</v>
@@ -3697,22 +3699,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
-        <v>42094</v>
+        <v>42004</v>
       </c>
       <c r="B137" s="1">
-        <v>0.47899999999999998</v>
+        <v>1.1659999999999999</v>
       </c>
       <c r="C137" s="1">
-        <v>0.23</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="D137" s="1">
-        <v>-7.0000000000000007E-2</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="E137" s="1">
-        <v>-0.13500000000000001</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="F137" s="1">
-        <v>-0.1</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>5</v>
@@ -3721,22 +3723,22 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
-        <v>42062</v>
+        <v>41971</v>
       </c>
       <c r="B138" s="1">
-        <v>0.81299999999999994</v>
+        <v>1.335</v>
       </c>
       <c r="C138" s="1">
-        <v>0.46700000000000003</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="D138" s="1">
-        <v>2E-3</v>
+        <v>0.222</v>
       </c>
       <c r="E138" s="1">
-        <v>-9.8000000000000004E-2</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="F138" s="1">
-        <v>-7.9000000000000001E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>5</v>
@@ -3745,22 +3747,22 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
-        <v>42034</v>
+        <v>41943</v>
       </c>
       <c r="B139" s="1">
-        <v>0.88400000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="C139" s="1">
-        <v>0.55700000000000005</v>
+        <v>1.0449999999999999</v>
       </c>
       <c r="D139" s="1">
-        <v>0.115</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="E139" s="1">
-        <v>4.9000000000000002E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="F139" s="1">
-        <v>4.2000000000000003E-2</v>
+        <v>6.2E-2</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>5</v>
@@ -3769,22 +3771,22 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
-        <v>42004</v>
+        <v>41912</v>
       </c>
       <c r="B140" s="1">
-        <v>1.1659999999999999</v>
+        <v>1.6339999999999999</v>
       </c>
       <c r="C140" s="1">
-        <v>0.76500000000000001</v>
+        <v>1.129</v>
       </c>
       <c r="D140" s="1">
-        <v>0.17499999999999999</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="E140" s="1">
-        <v>6.5000000000000002E-2</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="F140" s="1">
-        <v>4.2999999999999997E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>5</v>
@@ -3793,22 +3795,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
-        <v>41971</v>
+        <v>41880</v>
       </c>
       <c r="B141" s="1">
-        <v>1.335</v>
+        <v>1.508</v>
       </c>
       <c r="C141" s="1">
-        <v>0.89500000000000002</v>
+        <v>1.0760000000000001</v>
       </c>
       <c r="D141" s="1">
-        <v>0.222</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="E141" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.127</v>
       </c>
       <c r="F141" s="1">
-        <v>5.8999999999999997E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>5</v>
@@ -3817,22 +3819,22 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
-        <v>41943</v>
+        <v>41851</v>
       </c>
       <c r="B142" s="1">
-        <v>1.53</v>
+        <v>1.8759999999999999</v>
       </c>
       <c r="C142" s="1">
-        <v>1.0449999999999999</v>
+        <v>1.3879999999999999</v>
       </c>
       <c r="D142" s="1">
-        <v>0.27200000000000002</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="E142" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="F142" s="1">
-        <v>6.2E-2</v>
+        <v>0.104</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>5</v>
@@ -3841,22 +3843,22 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
-        <v>41912</v>
+        <v>41820</v>
       </c>
       <c r="B143" s="1">
-        <v>1.6339999999999999</v>
+        <v>2.0009999999999999</v>
       </c>
       <c r="C143" s="1">
-        <v>1.129</v>
+        <v>1.492</v>
       </c>
       <c r="D143" s="1">
-        <v>0.27700000000000002</v>
+        <v>0.53</v>
       </c>
       <c r="E143" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="F143" s="1">
-        <v>5.5E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>5</v>
@@ -3865,22 +3867,22 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
-        <v>41880</v>
+        <v>41789</v>
       </c>
       <c r="B144" s="1">
-        <v>1.508</v>
+        <v>2.1349999999999998</v>
       </c>
       <c r="C144" s="1">
-        <v>1.0760000000000001</v>
+        <v>1.6319999999999999</v>
       </c>
       <c r="D144" s="1">
-        <v>0.33100000000000002</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="E144" s="1">
-        <v>0.127</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="F144" s="1">
-        <v>6.9000000000000006E-2</v>
+        <v>0.152</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>5</v>
@@ -3889,22 +3891,22 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
-        <v>41851</v>
+        <v>41759</v>
       </c>
       <c r="B145" s="1">
-        <v>1.8759999999999999</v>
+        <v>2.2970000000000002</v>
       </c>
       <c r="C145" s="1">
-        <v>1.3879999999999999</v>
+        <v>1.802</v>
       </c>
       <c r="D145" s="1">
-        <v>0.49399999999999999</v>
+        <v>0.80900000000000005</v>
       </c>
       <c r="E145" s="1">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="F145" s="1">
         <v>0.19900000000000001</v>
-      </c>
-      <c r="F145" s="1">
-        <v>0.104</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>5</v>
@@ -3913,22 +3915,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
-        <v>41820</v>
+        <v>41729</v>
       </c>
       <c r="B146" s="1">
-        <v>2.0009999999999999</v>
+        <v>2.39</v>
       </c>
       <c r="C146" s="1">
-        <v>1.492</v>
+        <v>1.889</v>
       </c>
       <c r="D146" s="1">
-        <v>0.53</v>
+        <v>0.876</v>
       </c>
       <c r="E146" s="1">
-        <v>0.19700000000000001</v>
+        <v>0.435</v>
       </c>
       <c r="F146" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>5</v>
@@ -3937,22 +3939,22 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
-        <v>41789</v>
+        <v>41698</v>
       </c>
       <c r="B147" s="1">
-        <v>2.1349999999999998</v>
+        <v>2.4569999999999999</v>
       </c>
       <c r="C147" s="1">
-        <v>1.6319999999999999</v>
+        <v>1.9530000000000001</v>
       </c>
       <c r="D147" s="1">
-        <v>0.64800000000000002</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="E147" s="1">
-        <v>0.27700000000000002</v>
+        <v>0.44800000000000001</v>
       </c>
       <c r="F147" s="1">
-        <v>0.152</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>5</v>
@@ -3961,22 +3963,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
-        <v>41759</v>
+        <v>41670</v>
       </c>
       <c r="B148" s="1">
-        <v>2.2970000000000002</v>
+        <v>2.488</v>
       </c>
       <c r="C148" s="1">
-        <v>1.802</v>
+        <v>1.982</v>
       </c>
       <c r="D148" s="1">
-        <v>0.80900000000000005</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="E148" s="1">
-        <v>0.38500000000000001</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="F148" s="1">
-        <v>0.19900000000000001</v>
+        <v>0.151</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>5</v>
@@ -3985,22 +3987,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
-        <v>41729</v>
+        <v>41639</v>
       </c>
       <c r="B149" s="1">
-        <v>2.39</v>
+        <v>2.722</v>
       </c>
       <c r="C149" s="1">
-        <v>1.889</v>
+        <v>2.2320000000000002</v>
       </c>
       <c r="D149" s="1">
-        <v>0.876</v>
+        <v>1.175</v>
       </c>
       <c r="E149" s="1">
-        <v>0.435</v>
+        <v>0.59</v>
       </c>
       <c r="F149" s="1">
-        <v>0.20399999999999999</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>5</v>
@@ -4009,22 +4011,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
-        <v>41698</v>
+        <v>41607</v>
       </c>
       <c r="B150" s="1">
-        <v>2.4569999999999999</v>
+        <v>2.5819999999999999</v>
       </c>
       <c r="C150" s="1">
-        <v>1.9530000000000001</v>
+        <v>2.0350000000000001</v>
       </c>
       <c r="D150" s="1">
-        <v>0.93899999999999995</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="E150" s="1">
-        <v>0.44800000000000001</v>
+        <v>0.372</v>
       </c>
       <c r="F150" s="1">
-        <v>0.16500000000000001</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>5</v>
@@ -4033,22 +4035,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
-        <v>41670</v>
+        <v>41578</v>
       </c>
       <c r="B151" s="1">
-        <v>2.488</v>
+        <v>2.58</v>
       </c>
       <c r="C151" s="1">
-        <v>1.982</v>
+        <v>2.0350000000000001</v>
       </c>
       <c r="D151" s="1">
-        <v>0.92800000000000005</v>
+        <v>0.94699999999999995</v>
       </c>
       <c r="E151" s="1">
-        <v>0.41299999999999998</v>
+        <v>0.434</v>
       </c>
       <c r="F151" s="1">
-        <v>0.151</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>5</v>
@@ -4057,22 +4059,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
-        <v>41639</v>
+        <v>41547</v>
       </c>
       <c r="B152" s="1">
-        <v>2.722</v>
+        <v>2.669</v>
       </c>
       <c r="C152" s="1">
-        <v>2.2320000000000002</v>
+        <v>2.161</v>
       </c>
       <c r="D152" s="1">
-        <v>1.175</v>
+        <v>1.0780000000000001</v>
       </c>
       <c r="E152" s="1">
-        <v>0.59</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="F152" s="1">
-        <v>0.17699999999999999</v>
+        <v>0.153</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>5</v>
@@ -4081,22 +4083,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
-        <v>41607</v>
+        <v>41516</v>
       </c>
       <c r="B153" s="1">
-        <v>2.5819999999999999</v>
+        <v>2.7559999999999998</v>
       </c>
       <c r="C153" s="1">
-        <v>2.0350000000000001</v>
+        <v>2.2389999999999999</v>
       </c>
       <c r="D153" s="1">
-        <v>0.90200000000000002</v>
+        <v>1.1870000000000001</v>
       </c>
       <c r="E153" s="1">
-        <v>0.372</v>
+        <v>0.61</v>
       </c>
       <c r="F153" s="1">
-        <v>0.11899999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>5</v>
@@ -4105,22 +4107,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
-        <v>41578</v>
+        <v>41486</v>
       </c>
       <c r="B154" s="1">
-        <v>2.58</v>
+        <v>2.6459999999999999</v>
       </c>
       <c r="C154" s="1">
-        <v>2.0350000000000001</v>
+        <v>2.1110000000000002</v>
       </c>
       <c r="D154" s="1">
-        <v>0.94699999999999995</v>
+        <v>1.052</v>
       </c>
       <c r="E154" s="1">
-        <v>0.434</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="F154" s="1">
-        <v>0.13500000000000001</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>5</v>
@@ -4129,22 +4131,22 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
-        <v>41547</v>
+        <v>41453</v>
       </c>
       <c r="B155" s="1">
-        <v>2.669</v>
+        <v>2.641</v>
       </c>
       <c r="C155" s="1">
-        <v>2.161</v>
+        <v>2.12</v>
       </c>
       <c r="D155" s="1">
-        <v>1.0780000000000001</v>
+        <v>1.1040000000000001</v>
       </c>
       <c r="E155" s="1">
-        <v>0.52500000000000002</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="F155" s="1">
-        <v>0.153</v>
+        <v>0.189</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>5</v>
@@ -4153,22 +4155,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
-        <v>41516</v>
+        <v>41425</v>
       </c>
       <c r="B156" s="1">
-        <v>2.7559999999999998</v>
+        <v>2.4279999999999999</v>
       </c>
       <c r="C156" s="1">
-        <v>2.2389999999999999</v>
+        <v>1.853</v>
       </c>
       <c r="D156" s="1">
-        <v>1.1870000000000001</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="E156" s="1">
-        <v>0.61</v>
+        <v>0.371</v>
       </c>
       <c r="F156" s="1">
-        <v>0.16</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>5</v>
@@ -4177,22 +4179,22 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
-        <v>41486</v>
+        <v>41394</v>
       </c>
       <c r="B157" s="1">
-        <v>2.6459999999999999</v>
+        <v>2.17</v>
       </c>
       <c r="C157" s="1">
-        <v>2.1110000000000002</v>
+        <v>1.5980000000000001</v>
       </c>
       <c r="D157" s="1">
-        <v>1.052</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="E157" s="1">
-        <v>0.51900000000000002</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="F157" s="1">
-        <v>0.14899999999999999</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>5</v>
@@ -4201,22 +4203,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
-        <v>41453</v>
+        <v>41362</v>
       </c>
       <c r="B158" s="1">
-        <v>2.641</v>
+        <v>2.4079999999999999</v>
       </c>
       <c r="C158" s="1">
-        <v>2.12</v>
+        <v>1.855</v>
       </c>
       <c r="D158" s="1">
-        <v>1.1040000000000001</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="E158" s="1">
-        <v>0.58699999999999997</v>
+        <v>0.4</v>
       </c>
       <c r="F158" s="1">
-        <v>0.189</v>
+        <v>0.123</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>5</v>
@@ -4225,22 +4227,22 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
-        <v>41425</v>
+        <v>41333</v>
       </c>
       <c r="B159" s="1">
-        <v>2.4279999999999999</v>
+        <v>2.4820000000000002</v>
       </c>
       <c r="C159" s="1">
-        <v>1.853</v>
+        <v>1.921</v>
       </c>
       <c r="D159" s="1">
-        <v>0.82399999999999995</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="E159" s="1">
-        <v>0.371</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="F159" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>5</v>
@@ -4249,22 +4251,22 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
-        <v>41394</v>
+        <v>41305</v>
       </c>
       <c r="B160" s="1">
-        <v>2.17</v>
+        <v>2.548</v>
       </c>
       <c r="C160" s="1">
-        <v>1.5980000000000001</v>
+        <v>2.0790000000000002</v>
       </c>
       <c r="D160" s="1">
-        <v>0.60899999999999999</v>
+        <v>1.0960000000000001</v>
       </c>
       <c r="E160" s="1">
-        <v>0.23699999999999999</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="F160" s="1">
-        <v>7.0999999999999994E-2</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>5</v>
@@ -4273,22 +4275,22 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
-        <v>41362</v>
+        <v>41274</v>
       </c>
       <c r="B161" s="1">
-        <v>2.4079999999999999</v>
+        <v>2.2610000000000001</v>
       </c>
       <c r="C161" s="1">
-        <v>1.855</v>
+        <v>1.714</v>
       </c>
       <c r="D161" s="1">
-        <v>0.83099999999999996</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="E161" s="1">
-        <v>0.4</v>
+        <v>0.248</v>
       </c>
       <c r="F161" s="1">
-        <v>0.123</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>5</v>
@@ -4297,22 +4299,22 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
-        <v>41333</v>
+        <v>41243</v>
       </c>
       <c r="B162" s="1">
-        <v>2.4820000000000002</v>
+        <v>2.4140000000000001</v>
       </c>
       <c r="C162" s="1">
-        <v>1.921</v>
+        <v>1.847</v>
       </c>
       <c r="D162" s="1">
-        <v>0.83099999999999996</v>
+        <v>0.76400000000000001</v>
       </c>
       <c r="E162" s="1">
-        <v>0.35899999999999999</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="F162" s="1">
-        <v>0.08</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>5</v>
@@ -4321,22 +4323,22 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
-        <v>41305</v>
+        <v>41213</v>
       </c>
       <c r="B163" s="1">
-        <v>2.548</v>
+        <v>2.5169999999999999</v>
       </c>
       <c r="C163" s="1">
-        <v>2.0790000000000002</v>
+        <v>1.962</v>
       </c>
       <c r="D163" s="1">
-        <v>1.0960000000000001</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="E163" s="1">
-        <v>0.63900000000000001</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="F163" s="1">
-        <v>0.20300000000000001</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>5</v>
@@ -4345,22 +4347,22 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
-        <v>41274</v>
+        <v>41180</v>
       </c>
       <c r="B164" s="1">
-        <v>2.2610000000000001</v>
+        <v>2.4969999999999999</v>
       </c>
       <c r="C164" s="1">
-        <v>1.714</v>
+        <v>1.9750000000000001</v>
       </c>
       <c r="D164" s="1">
-        <v>0.66100000000000003</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="E164" s="1">
-        <v>0.248</v>
+        <v>0.37</v>
       </c>
       <c r="F164" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>5</v>
@@ -4369,22 +4371,22 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
-        <v>41243</v>
+        <v>41152</v>
       </c>
       <c r="B165" s="1">
-        <v>2.4140000000000001</v>
+        <v>2.4420000000000002</v>
       </c>
       <c r="C165" s="1">
-        <v>1.847</v>
+        <v>1.93</v>
       </c>
       <c r="D165" s="1">
-        <v>0.76400000000000001</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="E165" s="1">
-        <v>0.28999999999999998</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="F165" s="1">
-        <v>7.3999999999999996E-2</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>5</v>
@@ -4393,22 +4395,22 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
-        <v>41213</v>
+        <v>41121</v>
       </c>
       <c r="B166" s="1">
-        <v>2.5169999999999999</v>
+        <v>2.5840000000000001</v>
       </c>
       <c r="C166" s="1">
-        <v>1.962</v>
+        <v>2.0819999999999999</v>
       </c>
       <c r="D166" s="1">
-        <v>0.86199999999999999</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="E166" s="1">
         <v>0.36899999999999999</v>
       </c>
       <c r="F166" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>5</v>
@@ -4417,22 +4419,22 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
-        <v>41180</v>
+        <v>41089</v>
       </c>
       <c r="B167" s="1">
-        <v>2.4969999999999999</v>
+        <v>2.93</v>
       </c>
       <c r="C167" s="1">
-        <v>1.9750000000000001</v>
+        <v>2.4660000000000002</v>
       </c>
       <c r="D167" s="1">
-        <v>0.86899999999999999</v>
+        <v>1.3720000000000001</v>
       </c>
       <c r="E167" s="1">
-        <v>0.37</v>
+        <v>0.76600000000000001</v>
       </c>
       <c r="F167" s="1">
-        <v>0.13100000000000001</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>5</v>
@@ -4441,22 +4443,22 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
-        <v>41152</v>
+        <v>41060</v>
       </c>
       <c r="B168" s="1">
-        <v>2.4420000000000002</v>
+        <v>2.5259999999999998</v>
       </c>
       <c r="C168" s="1">
-        <v>1.93</v>
+        <v>2.1880000000000002</v>
       </c>
       <c r="D168" s="1">
-        <v>0.79400000000000004</v>
+        <v>1.2509999999999999</v>
       </c>
       <c r="E168" s="1">
-        <v>0.26700000000000002</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="F168" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.53</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>5</v>
@@ -4465,22 +4467,22 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
-        <v>41121</v>
+        <v>41029</v>
       </c>
       <c r="B169" s="1">
-        <v>2.5840000000000001</v>
+        <v>3.153</v>
       </c>
       <c r="C169" s="1">
-        <v>2.0819999999999999</v>
+        <v>2.6890000000000001</v>
       </c>
       <c r="D169" s="1">
-        <v>0.94899999999999995</v>
+        <v>1.5289999999999999</v>
       </c>
       <c r="E169" s="1">
-        <v>0.36899999999999999</v>
+        <v>0.90800000000000003</v>
       </c>
       <c r="F169" s="1">
-        <v>0.11600000000000001</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>5</v>
@@ -4489,22 +4491,22 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
-        <v>41089</v>
+        <v>40998</v>
       </c>
       <c r="B170" s="1">
-        <v>2.93</v>
+        <v>3.113</v>
       </c>
       <c r="C170" s="1">
-        <v>2.4660000000000002</v>
+        <v>2.7080000000000002</v>
       </c>
       <c r="D170" s="1">
-        <v>1.3720000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="E170" s="1">
-        <v>0.76600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="F170" s="1">
-        <v>0.46200000000000002</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>5</v>
@@ -4513,22 +4515,22 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
-        <v>41060</v>
+        <v>40968</v>
       </c>
       <c r="B171" s="1">
-        <v>2.5259999999999998</v>
+        <v>3.1589999999999998</v>
       </c>
       <c r="C171" s="1">
-        <v>2.1880000000000002</v>
+        <v>2.7730000000000001</v>
       </c>
       <c r="D171" s="1">
-        <v>1.2509999999999999</v>
+        <v>1.758</v>
       </c>
       <c r="E171" s="1">
-        <v>0.76300000000000001</v>
+        <v>1.165</v>
       </c>
       <c r="F171" s="1">
-        <v>0.53</v>
+        <v>0.94</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>5</v>
@@ -4537,22 +4539,22 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
-        <v>41029</v>
+        <v>40939</v>
       </c>
       <c r="B172" s="1">
-        <v>3.153</v>
+        <v>3.1560000000000001</v>
       </c>
       <c r="C172" s="1">
-        <v>2.6890000000000001</v>
+        <v>2.8140000000000001</v>
       </c>
       <c r="D172" s="1">
-        <v>1.5289999999999999</v>
+        <v>1.8879999999999999</v>
       </c>
       <c r="E172" s="1">
-        <v>0.90800000000000003</v>
+        <v>1.3420000000000001</v>
       </c>
       <c r="F172" s="1">
-        <v>0.61699999999999999</v>
+        <v>1.226</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>5</v>
@@ -4561,22 +4563,22 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
-        <v>40998</v>
+        <v>40907</v>
       </c>
       <c r="B173" s="1">
-        <v>3.113</v>
+        <v>3.2109999999999999</v>
       </c>
       <c r="C173" s="1">
-        <v>2.7080000000000002</v>
+        <v>2.895</v>
       </c>
       <c r="D173" s="1">
-        <v>1.66</v>
+        <v>2.1219999999999999</v>
       </c>
       <c r="E173" s="1">
-        <v>1.06</v>
+        <v>1.635</v>
       </c>
       <c r="F173" s="1">
-        <v>0.72199999999999998</v>
+        <v>1.554</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>5</v>
@@ -4585,22 +4587,22 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
-        <v>40968</v>
+        <v>40877</v>
       </c>
       <c r="B174" s="1">
-        <v>3.1589999999999998</v>
+        <v>3.7440000000000002</v>
       </c>
       <c r="C174" s="1">
-        <v>2.7730000000000001</v>
+        <v>3.4239999999999999</v>
       </c>
       <c r="D174" s="1">
-        <v>1.758</v>
+        <v>2.5289999999999999</v>
       </c>
       <c r="E174" s="1">
-        <v>1.165</v>
+        <v>1.863</v>
       </c>
       <c r="F174" s="1">
-        <v>0.94</v>
+        <v>1.657</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>5</v>
@@ -4609,22 +4611,22 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
-        <v>40939</v>
+        <v>40847</v>
       </c>
       <c r="B175" s="1">
-        <v>3.1560000000000001</v>
+        <v>3.2839999999999998</v>
       </c>
       <c r="C175" s="1">
-        <v>2.8140000000000001</v>
+        <v>2.9209999999999998</v>
       </c>
       <c r="D175" s="1">
-        <v>1.8879999999999999</v>
+        <v>2.1040000000000001</v>
       </c>
       <c r="E175" s="1">
-        <v>1.3420000000000001</v>
+        <v>1.5660000000000001</v>
       </c>
       <c r="F175" s="1">
-        <v>1.226</v>
+        <v>1.4510000000000001</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>5</v>
@@ -4633,22 +4635,22 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
-        <v>40907</v>
+        <v>40816</v>
       </c>
       <c r="B176" s="1">
-        <v>3.2109999999999999</v>
+        <v>3.13</v>
       </c>
       <c r="C176" s="1">
-        <v>2.895</v>
+        <v>2.7639999999999998</v>
       </c>
       <c r="D176" s="1">
-        <v>2.1219999999999999</v>
+        <v>2.0169999999999999</v>
       </c>
       <c r="E176" s="1">
-        <v>1.635</v>
+        <v>1.5029999999999999</v>
       </c>
       <c r="F176" s="1">
-        <v>1.554</v>
+        <v>1.42</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>5</v>
@@ -4657,22 +4659,22 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
-        <v>40877</v>
+        <v>40786</v>
       </c>
       <c r="B177" s="1">
-        <v>3.7440000000000002</v>
+        <v>3.4220000000000002</v>
       </c>
       <c r="C177" s="1">
-        <v>3.4239999999999999</v>
+        <v>2.956</v>
       </c>
       <c r="D177" s="1">
-        <v>2.5289999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="E177" s="1">
-        <v>1.863</v>
+        <v>1.571</v>
       </c>
       <c r="F177" s="1">
-        <v>1.657</v>
+        <v>1.425</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>5</v>
@@ -4681,22 +4683,22 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
-        <v>40847</v>
+        <v>40753</v>
       </c>
       <c r="B178" s="1">
-        <v>3.2839999999999998</v>
+        <v>3.6970000000000001</v>
       </c>
       <c r="C178" s="1">
-        <v>2.9209999999999998</v>
+        <v>3.2759999999999998</v>
       </c>
       <c r="D178" s="1">
-        <v>2.1040000000000001</v>
+        <v>2.488</v>
       </c>
       <c r="E178" s="1">
-        <v>1.5660000000000001</v>
+        <v>1.9510000000000001</v>
       </c>
       <c r="F178" s="1">
-        <v>1.4510000000000001</v>
+        <v>1.712</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>5</v>
@@ -4705,22 +4707,22 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
-        <v>40816</v>
+        <v>40724</v>
       </c>
       <c r="B179" s="1">
-        <v>3.13</v>
+        <v>4.0060000000000002</v>
       </c>
       <c r="C179" s="1">
-        <v>2.7639999999999998</v>
+        <v>3.5569999999999999</v>
       </c>
       <c r="D179" s="1">
-        <v>2.0169999999999999</v>
+        <v>2.8290000000000002</v>
       </c>
       <c r="E179" s="1">
-        <v>1.5029999999999999</v>
+        <v>2.2879999999999998</v>
       </c>
       <c r="F179" s="1">
-        <v>1.42</v>
+        <v>1.847</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>5</v>
@@ -4729,22 +4731,22 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
-        <v>40786</v>
+        <v>40694</v>
       </c>
       <c r="B180" s="1">
-        <v>3.4220000000000002</v>
+        <v>3.88</v>
       </c>
       <c r="C180" s="1">
-        <v>2.956</v>
+        <v>3.468</v>
       </c>
       <c r="D180" s="1">
-        <v>2.14</v>
+        <v>2.7519999999999998</v>
       </c>
       <c r="E180" s="1">
-        <v>1.571</v>
+        <v>2.2509999999999999</v>
       </c>
       <c r="F180" s="1">
-        <v>1.425</v>
+        <v>1.784</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>5</v>
@@ -4753,99 +4755,27 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
-        <v>40753</v>
+        <v>40662</v>
       </c>
       <c r="B181" s="1">
-        <v>3.6970000000000001</v>
+        <v>4.0759999999999996</v>
       </c>
       <c r="C181" s="1">
-        <v>3.2759999999999998</v>
+        <v>3.6869999999999998</v>
       </c>
       <c r="D181" s="1">
-        <v>2.488</v>
+        <v>2.9940000000000002</v>
       </c>
       <c r="E181" s="1">
-        <v>1.9510000000000001</v>
+        <v>2.5139999999999998</v>
       </c>
       <c r="F181" s="1">
-        <v>1.712</v>
+        <v>1.8620000000000001</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H181" s="1"/>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A182" s="2">
-        <v>40724</v>
-      </c>
-      <c r="B182" s="1">
-        <v>4.0060000000000002</v>
-      </c>
-      <c r="C182" s="1">
-        <v>3.5569999999999999</v>
-      </c>
-      <c r="D182" s="1">
-        <v>2.8290000000000002</v>
-      </c>
-      <c r="E182" s="1">
-        <v>2.2879999999999998</v>
-      </c>
-      <c r="F182" s="1">
-        <v>1.847</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H182" s="1"/>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A183" s="2">
-        <v>40694</v>
-      </c>
-      <c r="B183" s="1">
-        <v>3.88</v>
-      </c>
-      <c r="C183" s="1">
-        <v>3.468</v>
-      </c>
-      <c r="D183" s="1">
-        <v>2.7519999999999998</v>
-      </c>
-      <c r="E183" s="1">
-        <v>2.2509999999999999</v>
-      </c>
-      <c r="F183" s="1">
-        <v>1.784</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H183" s="1"/>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A184" s="2">
-        <v>40662</v>
-      </c>
-      <c r="B184" s="1">
-        <v>4.0759999999999996</v>
-      </c>
-      <c r="C184" s="1">
-        <v>3.6869999999999998</v>
-      </c>
-      <c r="D184" s="1">
-        <v>2.9940000000000002</v>
-      </c>
-      <c r="E184" s="1">
-        <v>2.5139999999999998</v>
-      </c>
-      <c r="F184" s="1">
-        <v>1.8620000000000001</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H184" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
